--- a/evaluation/baseline/baseline.xlsx
+++ b/evaluation/baseline/baseline.xlsx
@@ -8,24 +8,57 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IT\THI\PAPER\project\neurosymbolic-legal-reasoner\evaluation\baseline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F56269C-4294-4F1C-AFF2-D18783A857CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C327FDF4-6C58-461F-BA94-C012F3E95451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="80">
   <si>
     <t>Model</t>
   </si>
@@ -222,62 +255,450 @@
     <t xml:space="preserve"> Xin luật sư cho tôi hỏi: mua lại công ty đang hoạt động thì người nhận chuyển nhượng cần kiểm tra rủi ro thuế gì? </t>
   </si>
   <si>
-    <t>✅ Chạy được. Checkpoint HuggingFace công khai, có thể inference bằng Transformers/vLLM. Đây là baseline Việt Nam quan trọng nhất.</t>
-  </si>
-  <si>
-    <t>✅ Chạy được. Checkpoint HF đầy đủ, cộng đồng sử dụng nhiều, dễ benchmark.</t>
-  </si>
-  <si>
-    <t>✅ Chạy được. Checkpoint public, kích thước nhỏ, dễ chạy nhất trong nhóm legal Trung Quốc.</t>
-  </si>
-  <si>
-    <t>✅ Chạy được. Checkpoint HF còn hoạt động, có thể benchmark trực tiếp.</t>
-  </si>
-  <si>
-    <t>⚠️ Chạy được nhưng khó. Repo còn tồn tại nhưng checkpoint chính thức thường đổi link hoặc bị gỡ. Có thể phải rebuild từ InternLM2 + dữ liệu paper.</t>
-  </si>
-  <si>
-    <t>⚠️ Chạy được nhưng khó. Có repo và một số checkpoint fork, cần xác định đúng phiên bản được dùng trong paper.</t>
-  </si>
-  <si>
-    <t>❌ Không chạy được. Model đóng (proprietary), không phát hành checkpoint.</t>
-  </si>
-  <si>
-    <t>⚠️ Chạy được nhưng khó. Repo công khai nhưng checkpoint không phải lúc nào cũng public đầy đủ. Có thể phải xin quyền hoặc tự dựng lại.</t>
-  </si>
-  <si>
-    <t>✅ Chạy được. HuggingFace collection công khai, có checkpoint tải được.</t>
-  </si>
-  <si>
-    <t>✅ Chạy được. HuggingFace chính thức, model ổn định, dễ benchmark.</t>
-  </si>
-  <si>
-    <t>⚠️ Chạy được nhưng rất nặng. Cần nhiều GPU (thường ≥4×A100 80GB hoặc tương đương). Không phù hợp máy cá nhân.</t>
-  </si>
-  <si>
-    <t>❌ Gần như không chạy được. Quá lớn, yêu cầu hạ tầng enterprise, không thực tế cho benchmark học thuật thông thường.</t>
-  </si>
-  <si>
-    <t>❌ Không chạy được. Hiện chủ yếu còn paper/repo, checkpoint public rất khó tìm hoặc không còn duy trì. Reviewer thường chấp nhận cite thay vì reproduce.</t>
-  </si>
-  <si>
-    <t>❌ Không chạy được. Không có checkpoint chuẩn duy nhất, tồn tại nhiều biến thể khác nhau nên khó tái lập thực nghiệm.</t>
-  </si>
-  <si>
-    <t>❌ Không chạy được. Nhiều phiên bản khác nhau, thiếu checkpoint chuẩn công khai.</t>
-  </si>
-  <si>
-    <t>❌ Không chạy được. Chủ yếu là framework/paper, không có checkpoint chuẩn để tái lập.</t>
-  </si>
-  <si>
-    <t>❌ Chạy được. Có checkpoint public. Tuy nhiên đây là BERT encoder, không phải generative LLM nên so sánh QA sinh văn bản sẽ không công bằng.</t>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>❌ Repo không còn truy cập được</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="9"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>✅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Có thể tải và chạy thực tế.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Là một trong những Legal LLM châu Âu dễ tiếp cận nhất, phù hợp cho nghiên cứu và tái lập thực nghiệm.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- Trả lời được bằng tiếng Việt,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> có cấu trúc rõ ràng. Tuy nhiên nội dung chưa bám sát quy định pháp luật Việt Nam và xuất hiện một số lập luận thiếu căn cứ pháp lý cụ thể.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>⚠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Có thể tải và chạy dễ dàng</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, nhưng đây là mô hình BERT cho phân loại/truy hồi thông tin pháp lý, không phải mô hình sinh câu trả lời như các Legal LLM khác nên không phù hợp để so sánh trực tiếp.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>⚠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Có thể tải được một số phiên bản</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, nhưng chưa có sự thống nhất về mô hình gốc được sử dụng trong nghiên cứu nên việc tái lập còn hạn chế.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>⚠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Nghiên cứu có công bố nhưng khó tái lập.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Một số phiên bản mô hình không còn được duy trì hoặc khó truy cập, gây khó khăn cho việc triển khai thực nghiệm.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>⚠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Có thể tải được nhưng rất khó triển khai.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Kích thước quá lớn, yêu cầu nhiều GPU chuyên dụng nên không phù hợp với môi trường nghiên cứu thông thường.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">❌ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Không phù hợp để chạy thực nghiệm.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Chủ yếu là framework hoặc ý tưởng nghiên cứu, chưa phát hành mô hình chuẩn để tái lập.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">❌ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Không thể chạy thực nghiệm.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Đây là mô hình đóng, không phát hành trọng số nên không thể triển khai hoặc kiểm chứng độc lập.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">❌ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Không phù hợp để chạy thực nghiệm.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Thiếu mô hình chuẩn và tài liệu tái lập rõ ràng.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">❌ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Không phù hợp để chạy thực nghiệm.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Chủ yếu tồn tại dưới dạng bài báo và mã nguồn nghiên cứu, chưa có mô hình công khai đầy đủ để tái lập kết quả.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">❌ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Không phù hợp để chạy thực nghiệm.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Có nhiều biến thể khác nhau, thiếu phiên bản chuẩn được công bố chính thức nên khó so sánh công bằng.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>⚠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Mô hình được phát hành đầy đủ với toàn bộ trọng số (14 shard safetensors), có thể tái lập thực nghiệm. Tuy nhiên kích thước 32B rất lớn nên yêu cầu tài nguyên tính toán cao và khó triển khai trên môi trường nghiên cứu.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="7"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>⚠️</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Thực tế không khả thi cho nghiên cứu cá nhân.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Dù mô hình được công bố, yêu cầu hạ tầng tính toán rất lớn và vượt quá khả năng triển khai.</t>
+    </r>
+  </si>
+  <si>
+    <t>❌ Chỉ có adapter, không phải model đầy đủ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -314,6 +735,54 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -364,17 +833,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -388,13 +848,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -402,6 +859,30 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -419,6 +900,70 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -687,401 +1232,456 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.109375" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" customWidth="1"/>
-    <col min="4" max="4" width="26.109375" customWidth="1"/>
-    <col min="5" max="5" width="29.6640625" customWidth="1"/>
-    <col min="6" max="6" width="33" customWidth="1"/>
-    <col min="7" max="7" width="41.109375" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="11"/>
+    <col min="2" max="2" width="26.109375" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" customWidth="1"/>
+    <col min="4" max="4" width="30.21875" customWidth="1"/>
+    <col min="5" max="5" width="26.109375" customWidth="1"/>
+    <col min="6" max="6" width="29.6640625" customWidth="1"/>
+    <col min="7" max="7" width="93.77734375" customWidth="1"/>
+    <col min="8" max="8" width="41.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="2"/>
     </row>
     <row r="2" spans="1:8" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" s="1" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="12" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="14">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="15" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
+    <row r="5" spans="1:8" s="12" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="12">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="D5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="3" t="s">
+      <c r="H5" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="14">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="12" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="12">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="14">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="12" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="12">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="14">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="12" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="12">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A12" s="14">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="12" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="12">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="12" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="12">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="147.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="14">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="13" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="1" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="1" t="s">
+    <row r="17" spans="1:8" s="12" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="12">
+        <v>16</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="H17" s="12" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="14">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="1" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="3" t="s">
+      <c r="G18" s="4"/>
+      <c r="H18" s="17" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="1" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="10" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="10" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="10" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="10" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D18" r:id="rId1" xr:uid="{B8F2AFA8-73EA-49F6-8AA0-77B7B6C3CDC8}"/>
-    <hyperlink ref="D17" r:id="rId2" xr:uid="{80F6DBCF-0F97-4453-87FA-D2D887703F5D}"/>
-    <hyperlink ref="D16" r:id="rId3" xr:uid="{10042293-1522-4809-B91E-9D48660B3B70}"/>
-    <hyperlink ref="D14" r:id="rId4" xr:uid="{4B18B720-DDD8-45B6-A19A-57CD55FDE637}"/>
-    <hyperlink ref="D13" r:id="rId5" xr:uid="{BC89CC25-C556-470B-BF53-6C2CC14C5ADF}"/>
-    <hyperlink ref="D11" r:id="rId6" display="https://www.hkgai.org/" xr:uid="{87B319F4-F151-42A4-9523-217D9F295E74}"/>
-    <hyperlink ref="D7" r:id="rId7" xr:uid="{C620E5B9-4427-4180-BF0E-E052E089CDAA}"/>
-    <hyperlink ref="D6" r:id="rId8" display="https://github.com/InternLM/InternLM-Law?utm_source=chatgpt.com" xr:uid="{9C5805A2-9154-4F6C-84FB-4E8DA46C68E9}"/>
-    <hyperlink ref="D3" r:id="rId9" xr:uid="{FC865C46-33AA-45D7-84A7-B1E91BB7C49A}"/>
-    <hyperlink ref="D2" r:id="rId10" xr:uid="{C7689F0B-1D18-4F75-8EE9-3B8F188F0B01}"/>
+    <hyperlink ref="E18" r:id="rId1" xr:uid="{B8F2AFA8-73EA-49F6-8AA0-77B7B6C3CDC8}"/>
+    <hyperlink ref="E17" r:id="rId2" xr:uid="{80F6DBCF-0F97-4453-87FA-D2D887703F5D}"/>
+    <hyperlink ref="E16" r:id="rId3" xr:uid="{10042293-1522-4809-B91E-9D48660B3B70}"/>
+    <hyperlink ref="E14" r:id="rId4" xr:uid="{4B18B720-DDD8-45B6-A19A-57CD55FDE637}"/>
+    <hyperlink ref="E13" r:id="rId5" xr:uid="{BC89CC25-C556-470B-BF53-6C2CC14C5ADF}"/>
+    <hyperlink ref="E11" r:id="rId6" display="https://www.hkgai.org/" xr:uid="{87B319F4-F151-42A4-9523-217D9F295E74}"/>
+    <hyperlink ref="E7" r:id="rId7" xr:uid="{C620E5B9-4427-4180-BF0E-E052E089CDAA}"/>
+    <hyperlink ref="E6" r:id="rId8" display="https://github.com/InternLM/InternLM-Law?utm_source=chatgpt.com" xr:uid="{9C5805A2-9154-4F6C-84FB-4E8DA46C68E9}"/>
+    <hyperlink ref="E3" r:id="rId9" xr:uid="{FC865C46-33AA-45D7-84A7-B1E91BB7C49A}"/>
+    <hyperlink ref="E2" r:id="rId10" xr:uid="{C7689F0B-1D18-4F75-8EE9-3B8F188F0B01}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId11"/>
